--- a/comprehensive_analysis_gs64_no_lora_360m.xlsx
+++ b/comprehensive_analysis_gs64_no_lora_360m.xlsx
@@ -62,14 +62,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -635,7 +635,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -652,16 +652,16 @@
         <v>2.069916248321533</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2.295390605926514</v>
+        <v>1.254305362701416</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1089292176858917</v>
+        <v>0.3940308629788692</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -678,16 +678,16 @@
         <v>2.222823619842529</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2.014636516571045</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0.0936588496779753</v>
+        <v>0.8395440578460693</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.622307388516258</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -704,16 +704,16 @@
         <v>2.121335029602051</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2.442120552062988</v>
+        <v>1.230266571044922</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1512186985952496</v>
+        <v>0.4200507916584433</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>2.122696876525879</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1.856728792190552</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0.1252972514712627</v>
+        <v>0.8926413059234619</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.5794777314675248</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -756,16 +756,16 @@
         <v>2.069916248321533</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2.160919666290283</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>-0.04396478265366699</v>
+        <v>2.295390605926514</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-0.1089292176858917</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -782,16 +782,16 @@
         <v>2.222823619842529</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2.164241552352905</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.02635479799957053</v>
+        <v>2.014636516571045</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.0936588496779753</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -808,16 +808,16 @@
         <v>2.121335029602051</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2.128689289093018</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>-0.003466807170174534</v>
+        <v>2.442120552062988</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-0.1512186985952496</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -834,16 +834,16 @@
         <v>2.122696876525879</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1.930515050888061</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.09053663184936364</v>
+        <v>1.856728792190552</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.1252972514712627</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -860,16 +860,16 @@
         <v>2.069916248321533</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.6602330207824707</v>
+        <v>2.160919666290283</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.6810339445773013</v>
+        <v>-0.04396478265366699</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -886,16 +886,16 @@
         <v>2.222823619842529</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1.056910276412964</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0.5245190545132689</v>
+        <v>2.164241552352905</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.02635479799957053</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         <v>2.121335029602051</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.7126688957214355</v>
+        <v>2.128689289093018</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.6640469865549112</v>
+        <v>-0.003466807170174534</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -938,10 +938,10 @@
         <v>2.122696876525879</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.786644458770752</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0.6294127213970291</v>
+        <v>1.930515050888061</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.09053663184936364</v>
       </c>
     </row>
   </sheetData>
@@ -1132,7 +1132,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1149,16 +1149,16 @@
         <v>2.718506813049316</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2.669891357421875</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.01788314651045882</v>
+        <v>1.360885143280029</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.4993997672738805</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1175,16 +1175,16 @@
         <v>3.014318227767944</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2.571879863739014</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0.1467789166894132</v>
+        <v>0.7596487998962402</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.747986528795021</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1201,16 +1201,16 @@
         <v>2.508376598358154</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2.922121047973633</v>
+        <v>1.249581813812256</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1649451082769202</v>
+        <v>0.501836440895612</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1227,16 +1227,16 @@
         <v>2.515347242355347</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2.001346826553345</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0.2043457090722381</v>
+        <v>0.8353455066680908</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.6679005218039473</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1253,16 +1253,16 @@
         <v>2.718506813049316</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2.298252582550049</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0.1545900964757463</v>
+        <v>2.669891357421875</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.01788314651045882</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1279,16 +1279,16 @@
         <v>3.014318227767944</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2.294384241104126</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.2388380828645681</v>
+        <v>2.571879863739014</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.1467789166894132</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,16 +1305,16 @@
         <v>2.508376598358154</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2.278536319732666</v>
+        <v>2.922121047973633</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.09162909539816673</v>
+        <v>-0.1649451082769202</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1331,16 +1331,16 @@
         <v>2.515347242355347</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1.928260564804077</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.233401841171451</v>
+        <v>2.001346826553345</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.2043457090722381</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1357,16 +1357,16 @@
         <v>2.718506813049316</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.052669525146484</v>
+        <v>2.298252582550049</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1229214179244015</v>
+        <v>0.1545900964757463</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1383,16 +1383,16 @@
         <v>3.014318227767944</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.9925665855407716</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0.6707160589757135</v>
+        <v>2.294384241104126</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.2388380828645681</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1409,16 +1409,16 @@
         <v>2.508376598358154</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>3.050755977630615</v>
+        <v>2.278536319732666</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2162272521707756</v>
+        <v>0.09162909539816673</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1435,10 +1435,10 @@
         <v>2.515347242355347</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1.370407819747925</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0.4551814569885436</v>
+        <v>1.928260564804077</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.233401841171451</v>
       </c>
     </row>
   </sheetData>
@@ -1629,7 +1629,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1648,14 +1648,14 @@
       <c r="E8" s="3" t="n">
         <v>0.0195964813232421</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="4" t="n">
         <v>0.1941298277539011</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1674,14 +1674,14 @@
       <c r="E9" s="3" t="n">
         <v>0.0026344299316406</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="4" t="n">
         <v>0.1830602708936967</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1698,16 +1698,16 @@
         <v>0.0248912811279296</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.0239013442993164</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.03977042497432674</v>
+        <v>0.0201705932617187</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.1896522658656564</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1726,14 +1726,14 @@
       <c r="E11" s="3" t="n">
         <v>0.0072443008422851</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="4" t="n">
         <v>0.2503148279006619</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1750,16 +1750,16 @@
         <v>0.0243171691894531</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.0195979118347167</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0.1940710005333699</v>
+        <v>0.0195964813232421</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.1941298277539011</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1776,16 +1776,16 @@
         <v>0.003224754333496</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.0026358604431152</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.1826166676524385</v>
+        <v>0.0026344299316406</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.1830602708936967</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1802,16 +1802,16 @@
         <v>0.0248912811279296</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.0201720237731933</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0.1895947954820612</v>
+        <v>0.0239013442993164</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.03977042497432674</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1828,16 +1828,16 @@
         <v>0.009663124084472599</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.0072457313537597</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.25016678970286</v>
+        <v>0.0072443008422851</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.2503148279006619</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1854,16 +1854,16 @@
         <v>0.0243171691894531</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.0195964813232421</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0.1941298277539011</v>
+        <v>0.0195979118347167</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.1940710005333699</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1880,16 +1880,16 @@
         <v>0.003224754333496</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.0026344299316406</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0.1830602708936967</v>
+        <v>0.0026358604431152</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.1826166676524385</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1906,16 +1906,16 @@
         <v>0.0248912811279296</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.0201705932617187</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>0.1896522658656564</v>
+        <v>0.0201720237731933</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.1895947954820612</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1932,10 +1932,10 @@
         <v>0.009663124084472599</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.0072443008422851</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0.2503148279006619</v>
+        <v>0.0072457313537597</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.25016678970286</v>
       </c>
     </row>
   </sheetData>
@@ -2126,7 +2126,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2143,16 +2143,16 @@
         <v>0.0559415817260742</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.0422086715698242</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.2454866260931827</v>
+        <v>0.0241127014160156</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.5689663990180537</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2169,16 +2169,16 @@
         <v>0.0071773529052734</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.0054607391357421</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0.2391708743024265</v>
+        <v>0.0031991004943847</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.5542785011958611</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2195,16 +2195,16 @@
         <v>0.0565156936645507</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.0419341659545898</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.258008471001164</v>
+        <v>0.0246868133544921</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.5631865813941723</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>cuda_no_lora_360m_bwd_opt</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2221,16 +2221,16 @@
         <v>0.0215210914611816</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.0163712501525878</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0.2392927569627573</v>
+        <v>0.008936882019042899</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.5847384397226001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2247,16 +2247,16 @@
         <v>0.0559415817260742</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.0329837799072265</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0.4103888576348054</v>
+        <v>0.0422086715698242</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.2454866260931827</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2273,16 +2273,16 @@
         <v>0.0071773529052734</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.0043091773986816</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.3996146691469598</v>
+        <v>0.0054607391357421</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.2391708743024265</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2299,16 +2299,16 @@
         <v>0.0565156936645507</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.0335578918457031</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0.4062199422891949</v>
+        <v>0.0419341659545898</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.258008471001164</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>compile_no_lora_360m</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2325,16 +2325,16 @@
         <v>0.0215210914611816</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.0122642517089843</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.4301287306405536</v>
+        <v>0.0163712501525878</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.2392927569627573</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2351,16 +2351,16 @@
         <v>0.0559415817260742</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.0244703292846679</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0.5625735181302113</v>
+        <v>0.0329837799072265</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.4103888576348054</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2377,16 +2377,16 @@
         <v>0.0071773529052734</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.003244400024414</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0.5479670475684358</v>
+        <v>0.0043091773986816</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.3996146691469598</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2403,16 +2403,16 @@
         <v>0.0565156936645507</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.0250444412231445</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>0.5568586422773829</v>
+        <v>0.0335578918457031</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.4062199422891949</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m</t>
+          <t>triton_no</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2429,10 +2429,10 @@
         <v>0.0215210914611816</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.009071826934814399</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0.578468083220705</v>
+        <v>0.0122642517089843</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.4301287306405536</v>
       </c>
     </row>
   </sheetData>

--- a/comprehensive_analysis_gs64_no_lora_360m.xlsx
+++ b/comprehensive_analysis_gs64_no_lora_360m.xlsx
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -96,6 +96,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,15 +462,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,7 +516,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -529,7 +530,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.122696876525879</v>
+        <v>1.892782211303711</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -545,7 +546,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -559,7 +560,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.222823619842529</v>
+        <v>2.367697954177856</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -575,7 +576,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -589,7 +590,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.069916248321533</v>
+        <v>2.346645355224609</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -605,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -619,7 +620,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2.121335029602051</v>
+        <v>2.384308815002441</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -635,7 +636,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +650,19 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2.069916248321533</v>
+        <v>2.346645355224609</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.254305362701416</v>
+        <v>0.916358470916748</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3940308629788692</v>
+        <v>0.6095027870843148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -675,19 +676,19 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2.222823619842529</v>
+        <v>2.367697954177856</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.8395440578460693</v>
+        <v>0.8247075080871582</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.622307388516258</v>
+        <v>0.6516838194534302</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -701,19 +702,19 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2.121335029602051</v>
+        <v>2.384308815002441</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.230266571044922</v>
+        <v>0.9071216583251952</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.4200507916584433</v>
+        <v>0.6195452314660563</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -727,19 +728,19 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2.122696876525879</v>
+        <v>1.892782211303711</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.8926413059234619</v>
+        <v>1.193869352340698</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5794777314675248</v>
+        <v>0.3692515994651151</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -753,19 +754,19 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2.069916248321533</v>
+        <v>2.346645355224609</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2.295390605926514</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>-0.1089292176858917</v>
+        <v>1.902085781097412</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.1894447207957617</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -779,19 +780,19 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2.222823619842529</v>
+        <v>2.367697954177856</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2.014636516571045</v>
+        <v>2.024075746536255</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.0936588496779753</v>
+        <v>0.1451292412679888</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -805,19 +806,19 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2.121335029602051</v>
+        <v>2.384308815002441</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2.442120552062988</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>-0.1512186985952496</v>
+        <v>1.981001853942872</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.1691504718356531</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,19 +832,19 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2.122696876525879</v>
+        <v>1.892782211303711</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1.856728792190552</v>
+        <v>1.858097314834595</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1252972514712627</v>
+        <v>0.01832482166304064</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -857,19 +858,19 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.069916248321533</v>
+        <v>2.346645355224609</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.160919666290283</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>-0.04396478265366699</v>
+        <v>0.7288656234741211</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.6894010329036883</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -883,19 +884,19 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>2.222823619842529</v>
+        <v>2.367697954177856</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2.164241552352905</v>
+        <v>1.071951627731323</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.02635479799957053</v>
+        <v>0.547259976366563</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -909,19 +910,19 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2.121335029602051</v>
+        <v>2.384308815002441</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2.128689289093018</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>-0.003466807170174534</v>
+        <v>0.7837605476379395</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.6712839617475739</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -935,13 +936,221 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2.122696876525879</v>
+        <v>1.892782211303711</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1.930515050888061</v>
+        <v>0.7771875858306885</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.09053663184936364</v>
+        <v>0.5893940775704052</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2560, 960</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.346645355224609</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.9133896827697754</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.6107679071589621</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>320, 960</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.367697954177856</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1.164109706878662</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.5083369038586344</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>960, 2560</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2.384308815002441</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.8770012855529785</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.6321779796162518</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>960, 960</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1.892782211303711</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.8857789039611816</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.5320228081861174</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2560, 960</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2.346645355224609</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1.078979015350342</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.5402036302809518</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>320, 960</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2.367697954177856</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.9304068088531494</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.6070415961582323</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>960, 2560</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2.384308815002441</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.9359827041625975</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.6074406560621471</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>960, 960</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1.892782211303711</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.7974178791046143</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.5787059523581592</v>
       </c>
     </row>
   </sheetData>
@@ -958,15 +1167,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1012,7 +1221,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1026,7 +1235,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.515347242355347</v>
+        <v>1.984607696533204</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1042,7 +1251,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1056,7 +1265,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3.014318227767944</v>
+        <v>2.698436975479126</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1072,7 +1281,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1086,7 +1295,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.718506813049316</v>
+        <v>2.646252632141113</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1102,7 +1311,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1116,7 +1325,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2.508376598358154</v>
+        <v>2.733634948730469</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1132,7 +1341,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1146,19 +1355,19 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2.718506813049316</v>
+        <v>2.646252632141113</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1.360885143280029</v>
+        <v>0.7818789482116699</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.4993997672738805</v>
+        <v>0.7045335208305328</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1172,19 +1381,19 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3.014318227767944</v>
+        <v>2.698436975479126</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.7596487998962402</v>
+        <v>0.7101755142211914</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.747986528795021</v>
+        <v>0.7368196772151423</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1198,19 +1407,19 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2.508376598358154</v>
+        <v>2.733634948730469</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.249581813812256</v>
+        <v>0.7926898002624512</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.501836440895612</v>
+        <v>0.7100235345503666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1224,19 +1433,19 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2.515347242355347</v>
+        <v>1.984607696533204</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.8353455066680908</v>
+        <v>0.8421947956085205</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6679005218039473</v>
+        <v>0.5756366373668197</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1250,19 +1459,19 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2.718506813049316</v>
+        <v>2.646252632141113</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2.669891357421875</v>
+        <v>2.051215171813965</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.01788314651045882</v>
+        <v>0.2248604132122098</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1276,19 +1485,19 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>3.014318227767944</v>
+        <v>2.698436975479126</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2.571879863739014</v>
+        <v>2.051503419876098</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1467789166894132</v>
+        <v>0.2397438077975345</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1302,19 +1511,19 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2.508376598358154</v>
+        <v>2.733634948730469</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2.922121047973633</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>-0.1649451082769202</v>
+        <v>2.171078205108643</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.2057907343784451</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1328,19 +1537,19 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2.515347242355347</v>
+        <v>1.984607696533204</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2.001346826553345</v>
+        <v>1.686392307281494</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2043457090722381</v>
+        <v>0.1502641503268605</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1354,19 +1563,19 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.718506813049316</v>
+        <v>2.646252632141113</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.298252582550049</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0.1545900964757463</v>
+        <v>2.789026260375977</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.05395313603121254</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1380,19 +1589,19 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3.014318227767944</v>
+        <v>2.698436975479126</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2.294384241104126</v>
+        <v>0.9472143650054932</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2388380828645681</v>
+        <v>0.6489766581124954</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1406,19 +1615,19 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2.508376598358154</v>
+        <v>2.733634948730469</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2.278536319732666</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>0.09162909539816673</v>
+        <v>2.804117202758789</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-0.0257833453808648</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,13 +1641,221 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2.515347242355347</v>
+        <v>1.984607696533204</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1.928260564804077</v>
+        <v>1.363641023635864</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.233401841171451</v>
+        <v>0.3128913961092007</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2560, 960</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2.646252632141113</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>2.810713768005371</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-0.06214869051681979</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>320, 960</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.698436975479126</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.8919720649719238</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.6694486204134718</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>960, 2560</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2.733634948730469</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2.81082010269165</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.02823535527193465</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>960, 960</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1.984607696533204</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1.398273944854736</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.295440631769543</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2560, 960</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2.646252632141113</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.8434810638427734</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.6812545206009665</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>320, 960</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2.698436975479126</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.7702891826629639</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.7145424593338172</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>960, 2560</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2.733634948730469</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.812309741973877</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.7028462990820619</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>960, 960</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1.984607696533204</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.7578530311584473</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.6181345902858802</v>
       </c>
     </row>
   </sheetData>
@@ -1455,7 +1872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1463,7 +1880,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1509,7 +1926,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1523,7 +1940,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.009663124084472599</v>
+        <v>0.0055276870727539</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1539,7 +1956,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1553,7 +1970,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.003224754333496</v>
+        <v>0.0020622253417968</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1569,7 +1986,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1583,7 +2000,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0243171691894531</v>
+        <v>0.0150188446044921</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1599,7 +2016,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1613,7 +2030,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.0248912811279296</v>
+        <v>0.0193046569824218</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1629,7 +2046,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1643,19 +2060,19 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.0243171691894531</v>
+        <v>0.0150188446044921</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.0195964813232421</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0.1941298277539011</v>
+        <v>0.0150188446044921</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1669,19 +2086,19 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.003224754333496</v>
+        <v>0.0020622253417968</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.0026344299316406</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0.1830602708936967</v>
+        <v>0.0020622253417968</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1695,19 +2112,19 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.0248912811279296</v>
+        <v>0.0193046569824218</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.0201705932617187</v>
+        <v>0.0155929565429687</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1896522658656564</v>
+        <v>0.1922696913409472</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1721,19 +2138,19 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.009663124084472599</v>
+        <v>0.0055276870727539</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.0072443008422851</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0.2503148279006619</v>
+        <v>0.0055276870727539</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1747,19 +2164,19 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.0243171691894531</v>
+        <v>0.0150188446044921</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.0195964813232421</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0.1941298277539011</v>
+        <v>0.0150202751159667</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-9.524777120146141e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1773,19 +2190,19 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.003224754333496</v>
+        <v>0.0020622253417968</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.0026344299316406</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0.1830602708936967</v>
+        <v>0.0020636558532714</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.0006936736958888504</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1799,19 +2216,19 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.0248912811279296</v>
+        <v>0.0193046569824218</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.0239013442993164</v>
+        <v>0.0155943870544433</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.03977042497432674</v>
+        <v>0.1921955894557957</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1825,19 +2242,19 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.009663124084472599</v>
+        <v>0.0055276870727539</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.0072443008422851</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0.2503148279006619</v>
+        <v>0.0055291175842285</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-0.000258790241880887</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1851,19 +2268,19 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.0243171691894531</v>
+        <v>0.0150188446044921</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.0195979118347167</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0.1940710005333699</v>
+        <v>0.0150188446044921</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1877,19 +2294,19 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.003224754333496</v>
+        <v>0.0020622253417968</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.0026358604431152</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>0.1826166676524385</v>
+        <v>0.0020622253417968</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1903,19 +2320,19 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.0248912811279296</v>
+        <v>0.0193046569824218</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.0201720237731933</v>
+        <v>0.0155929565429687</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.1895947954820612</v>
+        <v>0.1922696913409472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1929,13 +2346,221 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.009663124084472599</v>
+        <v>0.0055276870727539</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.0072457313537597</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0.25016678970286</v>
+        <v>0.0055276870727539</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2560, 960</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.0150188446044921</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.0150188446044921</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>320, 960</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.0020622253417968</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.0020622253417968</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>960, 2560</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.0193046569824218</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.0155929565429687</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.1922696913409472</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>960, 960</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.0055276870727539</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.0055276870727539</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2560, 960</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.0150188446044921</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.0150188446044921</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>320, 960</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.0020622253417968</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.0020622253417968</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>960, 2560</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0.0193046569824218</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.0155929565429687</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.1922696913409472</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>960, 960</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0.0055276870727539</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.0055276870727539</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1952,7 +2577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2006,7 +2631,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2020,7 +2645,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.0215210914611816</v>
+        <v>0.0140061378479003</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2036,7 +2661,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2050,7 +2675,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.0071773529052734</v>
+        <v>0.0048885345458984</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2066,7 +2691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2080,7 +2705,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0559415817260742</v>
+        <v>0.0376310348510742</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2096,7 +2721,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>benchmark_ref_no_lora_360m</t>
+          <t>COMPILE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2110,7 +2735,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.0565156936645507</v>
+        <v>0.0373392105102539</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2126,7 +2751,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2140,19 +2765,19 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.0559415817260742</v>
+        <v>0.0376310348510742</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.0241127014160156</v>
+        <v>0.0195350646972656</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.5689663990180537</v>
+        <v>0.4808788869459443</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2166,19 +2791,19 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.0071773529052734</v>
+        <v>0.0048885345458984</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.0031991004943847</v>
+        <v>0.002626895904541</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.5542785011958611</v>
+        <v>0.4626414358174006</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2192,19 +2817,19 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.0565156936645507</v>
+        <v>0.0373392105102539</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.0246868133544921</v>
+        <v>0.0201091766357421</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5631865813941723</v>
+        <v>0.4614461216254205</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cuda_no_lora_360m_bwd_opt</t>
+          <t>CUDA_opt</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2218,19 +2843,19 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.0215210914611816</v>
+        <v>0.0140061378479003</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.008936882019042899</v>
+        <v>0.0072202682495117</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5847384397226001</v>
+        <v>0.4844925611956539</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2244,19 +2869,19 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.0559415817260742</v>
+        <v>0.0376310348510742</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.0422086715698242</v>
+        <v>0.0284061431884765</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2454866260931827</v>
+        <v>0.2451405256088611</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2270,19 +2895,19 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.0071773529052734</v>
+        <v>0.0048885345458984</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.0054607391357421</v>
+        <v>0.0037369728088378</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2391708743024265</v>
+        <v>0.2355637924307579</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2296,19 +2921,19 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.0565156936645507</v>
+        <v>0.0373392105102539</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.0419341659545898</v>
+        <v>0.0289802551269531</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.258008471001164</v>
+        <v>0.2238653487599934</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>compile_no_lora_360m</t>
+          <t>TRITON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2322,19 +2947,19 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.0215210914611816</v>
+        <v>0.0140061378479003</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.0163712501525878</v>
+        <v>0.0105476379394531</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.2392927569627573</v>
+        <v>0.2469274503795972</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2348,19 +2973,19 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.0559415817260742</v>
+        <v>0.0376310348510742</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.0329837799072265</v>
+        <v>0.0198926925659179</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4103888576348054</v>
+        <v>0.4713753516308082</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2374,19 +2999,19 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.0071773529052734</v>
+        <v>0.0048885345458984</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.0043091773986816</v>
+        <v>0.0026721954345703</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3996146691469598</v>
+        <v>0.4533749512290269</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2400,19 +3025,19 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.0565156936645507</v>
+        <v>0.0373392105102539</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.0335578918457031</v>
+        <v>0.0204668045043945</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.4062199422891949</v>
+        <v>0.451868311495927</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>triton_no</t>
+          <t>CUDA_2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2426,13 +3051,221 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.0215210914611816</v>
+        <v>0.0140061378479003</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.0122642517089843</v>
+        <v>0.0073552131652832</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.4301287306405536</v>
+        <v>0.4748578626629867</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2560, 960</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.0376310348510742</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.0198926925659179</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.4713753516308082</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>320, 960</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.0048885345458984</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.0026721954345703</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.4533749512290269</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>960, 2560</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.0373392105102539</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.0204668045043945</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.451868311495927</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CUDA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>960, 960</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.0140061378479003</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.0073552131652832</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.4748578626629867</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2560, 960</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.0376310348510742</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.0195350646972656</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.4808788869459443</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>320, 960</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.0048885345458984</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.002626895904541</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.4626414358174006</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>960, 2560</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0.0373392105102539</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.0201091766357421</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.4614461216254205</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CUDA_opt_2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>WEIGHTS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>960, 960</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0.0140061378479003</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.0072202682495117</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.4844925611956539</v>
       </c>
     </row>
   </sheetData>
